--- a/data/hrm_sync_leave_5.xlsx
+++ b/data/hrm_sync_leave_5.xlsx
@@ -94,15 +94,12 @@
     <t>Thân Trọng Tuấn</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
+    <t>Đã duyệt</t>
   </si>
   <si>
     <t>07/09/2026</t>
   </si>
   <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
     <t>02228947</t>
   </si>
   <si>
@@ -115,7 +112,28 @@
     <t>Buổi chiều/半日休暇 - 午後に</t>
   </si>
   <si>
+    <t>27/08/2026</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
     <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>12/08/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>20/08/2026</t>
   </si>
   <si>
     <t>21/09/2026</t>
@@ -680,15 +698,15 @@
         <v>22</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -697,10 +715,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="8">
         <v>0.5</v>
@@ -709,7 +727,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -724,7 +742,7 @@
         <v>22</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
@@ -741,13 +759,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>20</v>
@@ -768,15 +786,15 @@
         <v>22</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -794,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>23</v>
@@ -812,56 +830,140 @@
         <v>22</v>
       </c>
       <c r="N7" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1">
+      <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="8"/>
+      <c r="B8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7"/>

--- a/data/hrm_sync_leave_5.xlsx
+++ b/data/hrm_sync_leave_5.xlsx
@@ -64,10 +64,10 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
+    <t>01920668</t>
+  </si>
+  <si>
+    <t>Hà Viết Thế Thiện</t>
   </si>
   <si>
     <t>Plastic Extrusion</t>
@@ -76,7 +76,7 @@
     <t>T Extrusion</t>
   </si>
   <si>
-    <t>28/09/2026</t>
+    <t>01/10/2026</t>
   </si>
   <si>
     <t>有給休暇 / Nghỉ phép năm</t>
@@ -95,54 +95,6 @@
   </si>
   <si>
     <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>07/09/2026</t>
-  </si>
-  <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>03/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
-    <t>27/08/2026</t>
-  </si>
-  <si>
-    <t>28/08/2026</t>
-  </si>
-  <si>
-    <t>25/09/2026</t>
-  </si>
-  <si>
-    <t>12/08/2026</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>02226596</t>
-  </si>
-  <si>
-    <t>Đoàn Văn Dương</t>
-  </si>
-  <si>
-    <t>20/08/2026</t>
-  </si>
-  <si>
-    <t>21/09/2026</t>
-  </si>
-  <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
-    <t>nghỉ phép sinh nhật</t>
   </si>
 </sst>
 </file>
@@ -658,312 +610,116 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="8"/>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="8">
-        <v>2</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="8"/>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8"/>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="8"/>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="8"/>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="8"/>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7"/>

--- a/data/hrm_sync_leave_5.xlsx
+++ b/data/hrm_sync_leave_5.xlsx
@@ -64,37 +64,55 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
+  </si>
+  <si>
     <t>01920668</t>
   </si>
   <si>
     <t>Hà Viết Thế Thiện</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
     <t>01/10/2026</t>
-  </si>
-  <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
   </si>
 </sst>
 </file>
@@ -610,36 +628,92 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="8"/>
+      <c r="A5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7"/>

--- a/data/hrm_sync_leave_5.xlsx
+++ b/data/hrm_sync_leave_5.xlsx
@@ -64,37 +64,58 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01920668</t>
+  </si>
+  <si>
+    <t>Hà Viết Thế Thiện</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
     <t>02224358</t>
   </si>
   <si>
     <t>Hoàng Trung Hiếu</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
     <t>09/10/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
   </si>
   <si>
     <t>02228947</t>
@@ -103,16 +124,10 @@
     <t>Phạm Lê Minh Tân</t>
   </si>
   <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
     <t>12/10/2026</t>
-  </si>
-  <si>
-    <t>01920668</t>
-  </si>
-  <si>
-    <t>Hà Viết Thế Thiện</t>
-  </si>
-  <si>
-    <t>01/10/2026</t>
   </si>
 </sst>
 </file>
@@ -691,13 +706,13 @@
         <v>31</v>
       </c>
       <c r="G5" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -716,36 +731,92 @@
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7"/>

--- a/data/hrm_sync_leave_5.xlsx
+++ b/data/hrm_sync_leave_5.xlsx
@@ -64,46 +64,61 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
     <t>01920668</t>
   </si>
   <si>
     <t>Hà Viết Thế Thiện</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
     <t>01/10/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
-  </si>
-  <si>
-    <t>09/10/2026</t>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
   </si>
   <si>
     <t>02226596</t>
@@ -116,18 +131,6 @@
   </si>
   <si>
     <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>12/10/2026</t>
   </si>
 </sst>
 </file>
@@ -732,10 +735,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -750,13 +753,13 @@
         <v>31</v>
       </c>
       <c r="G6" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>22</v>
@@ -776,10 +779,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -788,10 +791,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7" s="8">
         <v>1</v>
@@ -819,36 +822,92 @@
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7"/>
